--- a/2. Báo cáo - giấy tờ/1. Báo cáo/Bàn giao/Bàn giao linh kiện vỏ hộp VNSH03 VNET X-Force 160626.xlsx
+++ b/2. Báo cáo - giấy tờ/1. Báo cáo/Bàn giao/Bàn giao linh kiện vỏ hộp VNSH03 VNET X-Force 160626.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\1. Báo cáo\Bàn giao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49C0C8E6-BA03-46BE-82BA-658A33E20631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{768E42EF-D1BC-4A14-AB46-18237B73BD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{2A78EE38-ECEF-4E81-A2AE-B87A74495F92}"/>
   </bookViews>
@@ -327,6 +327,15 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -362,15 +371,6 @@
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -751,56 +751,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="12" t="s">
+      <c r="B1" s="14"/>
+      <c r="C1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="13" t="s">
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="15"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="18"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="16" t="s">
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="18"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="21"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="19" t="s">
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="21"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="24"/>
     </row>
     <row r="5" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
     </row>
     <row r="6" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8"/>
@@ -817,10 +817,10 @@
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="24"/>
+      <c r="F7" s="12"/>
     </row>
     <row r="8" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
@@ -891,42 +891,42 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22" t="s">
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="23"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23" t="s">
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="E7:F7"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A1:B4"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="C2:F2"/>
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="C4:F4"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="E7:F7"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.5" right="0.5" top="1" bottom="1" header="0.5" footer="0.5"/>
